--- a/data/trans_orig/P1001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34923</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58567</t>
+          <t>59614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92981</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652461</t>
+          <t>652625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673902</t>
+          <t>673078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629784</t>
+          <t>628737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653428</t>
+          <t>655453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1289382</t>
+          <t>1288861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1321050</t>
+          <t>1322715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43551</t>
+          <t>44794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73608</t>
+          <t>77662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>57107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92075</t>
+          <t>91995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>108636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156199</t>
+          <t>155197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>888192</t>
+          <t>884138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>918249</t>
+          <t>917006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>876318</t>
+          <t>876398</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910208</t>
+          <t>911286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1773994</t>
+          <t>1774996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1817834</t>
+          <t>1821557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36985</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64653</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74372</t>
+          <t>73948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>109851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119107</t>
+          <t>119015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163740</t>
+          <t>164223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613856</t>
+          <t>613205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641524</t>
+          <t>640627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573409</t>
+          <t>573990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609469</t>
+          <t>609893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1198610</t>
+          <t>1198127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1243243</t>
+          <t>1243335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>46980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77211</t>
+          <t>76144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88189</t>
+          <t>88290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126241</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142930</t>
+          <t>148349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195577</t>
+          <t>198406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>865011</t>
+          <t>866078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895069</t>
+          <t>895242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>912371</t>
+          <t>910371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950423</t>
+          <t>950322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1785257</t>
+          <t>1782428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1837904</t>
+          <t>1832485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>171962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>225005</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283244</t>
+          <t>285475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>354868</t>
+          <t>353205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +2155,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>516514</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>475327</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>557935</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>516514</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>472859</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>560462</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3051538</t>
+          <t>3047829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3104090</t>
+          <t>3104581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3024329</t>
+          <t>3025992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3095953</t>
+          <t>3093722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6139227</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6097806</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6180414</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6139227</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6095279</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6182882</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34773</t>
+          <t>35172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61404</t>
+          <t>62971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>87613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126387</t>
+          <t>126997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129902</t>
+          <t>131661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178832</t>
+          <t>182336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642065</t>
+          <t>640498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668696</t>
+          <t>668297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570663</t>
+          <t>570053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609021</t>
+          <t>609437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1221687</t>
+          <t>1218183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1270617</t>
+          <t>1268858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104291</t>
+          <t>102225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138876</t>
+          <t>140642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186800</t>
+          <t>188674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>217363</t>
+          <t>213839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276909</t>
+          <t>277072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912602</t>
+          <t>914668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>949158</t>
+          <t>951665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>845384</t>
+          <t>843510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>893308</t>
+          <t>891542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1772168</t>
+          <t>1772005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1831714</t>
+          <t>1835238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57897</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83652</t>
+          <t>83496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123361</t>
+          <t>124041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119163</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167690</t>
+          <t>169374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>699726</t>
+          <t>699925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728509</t>
+          <t>729147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652758</t>
+          <t>652078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>692467</t>
+          <t>692623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1366052</t>
+          <t>1364368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1414579</t>
+          <t>1413839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>55469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89940</t>
+          <t>87299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126020</t>
+          <t>129745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175276</t>
+          <t>176765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190828</t>
+          <t>194870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248058</t>
+          <t>252414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856862</t>
+          <t>859503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892084</t>
+          <t>891333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>875680</t>
+          <t>874191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>924936</t>
+          <t>921211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1749700</t>
+          <t>1745344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1806930</t>
+          <t>1802888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213601</t>
+          <t>211723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277081</t>
+          <t>274717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480563</t>
+          <t>480889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>566098</t>
+          <t>568669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>709853</t>
+          <t>710869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>815980</t>
+          <t>817586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3147707</t>
+          <t>3150071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3211187</t>
+          <t>3213065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2990211</t>
+          <t>2987640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3075746</t>
+          <t>3075420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6165117</t>
+          <t>6163511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6271244</t>
+          <t>6270228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>53008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68074</t>
+          <t>69801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102756</t>
+          <t>104882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103067</t>
+          <t>104836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145630</t>
+          <t>145970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621267</t>
+          <t>621792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>646508</t>
+          <t>647199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570083</t>
+          <t>567957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>604765</t>
+          <t>603038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1202009</t>
+          <t>1201669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1244572</t>
+          <t>1242803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>38342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65533</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105211</t>
+          <t>103609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>150808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150153</t>
+          <t>153276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204954</t>
+          <t>206071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>956898</t>
+          <t>956158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>984557</t>
+          <t>984089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892646</t>
+          <t>892105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>937702</t>
+          <t>939304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1860390</t>
+          <t>1859273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915191</t>
+          <t>1912068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61114</t>
+          <t>62376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122990</t>
+          <t>123675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124163</t>
+          <t>125298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172588</t>
+          <t>172204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>698438</t>
+          <t>697176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>726687</t>
+          <t>726205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662021</t>
+          <t>661336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701129</t>
+          <t>701931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1371975</t>
+          <t>1372359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1420400</t>
+          <t>1419265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55378</t>
+          <t>56606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>88795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97924</t>
+          <t>98989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144557</t>
+          <t>142255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162535</t>
+          <t>162994</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215872</t>
+          <t>214921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850708</t>
+          <t>848772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882189</t>
+          <t>880961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>899222</t>
+          <t>901524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945855</t>
+          <t>944790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1765474</t>
+          <t>1766425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1818811</t>
+          <t>1818352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181184</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236112</t>
+          <t>236610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>393719</t>
+          <t>390919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>471155</t>
+          <t>475836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>592027</t>
+          <t>595029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>686199</t>
+          <t>687165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3158238</t>
+          <t>3157740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3213166</t>
+          <t>3214462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3073387</t>
+          <t>3068706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3150823</t>
+          <t>3153623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6252693</t>
+          <t>6251727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6346865</t>
+          <t>6343863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60697</t>
+          <t>61149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84037</t>
+          <t>84833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91287</t>
+          <t>90919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124234</t>
+          <t>123266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586638</t>
+          <t>588180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>609929</t>
+          <t>610218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>591092</t>
+          <t>590296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>614432</t>
+          <t>613980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1186337</t>
+          <t>1187305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219284</t>
+          <t>1219652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69585</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91891</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125514</t>
+          <t>124205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102443</t>
+          <t>110231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184979</t>
+          <t>187596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1123279</t>
+          <t>1123297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1168050</t>
+          <t>1169597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>831948</t>
+          <t>833257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>865571</t>
+          <t>866292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1965347</t>
+          <t>1962730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2047883</t>
+          <t>2040095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44402</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>82571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>114702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97018</t>
+          <t>94343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>175610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625187</t>
+          <t>622109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660278</t>
+          <t>658810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>817080</t>
+          <t>818664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>889024</t>
+          <t>895868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1461904</t>
+          <t>1462436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1541028</t>
+          <t>1543703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39393</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69973</t>
+          <t>70827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107220</t>
+          <t>105297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155004</t>
+          <t>156024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158767</t>
+          <t>158660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216926</t>
+          <t>215668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855652</t>
+          <t>854798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886232</t>
+          <t>884591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>938838</t>
+          <t>937818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>986622</t>
+          <t>988545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1802541</t>
+          <t>1803799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1860700</t>
+          <t>1860807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153091</t>
+          <t>150804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230943</t>
+          <t>230107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>325389</t>
+          <t>323034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>436584</t>
+          <t>440327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516011</t>
+          <t>514146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>654703</t>
+          <t>652784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3227668</t>
+          <t>3228504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3305520</t>
+          <t>3307807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3223215</t>
+          <t>3219472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3334410</t>
+          <t>3336765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6463706</t>
+          <t>6465625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6602398</t>
+          <t>6604263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41387</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>59265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59648</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93502</t>
+          <t>94576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>652625</t>
+          <t>652737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673078</t>
+          <t>673135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628737</t>
+          <t>629086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655453</t>
+          <t>654540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288861</t>
+          <t>1287787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1322715</t>
+          <t>1321587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44794</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77662</t>
+          <t>74486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>91856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108636</t>
+          <t>108361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>152441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884138</t>
+          <t>887314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>917006</t>
+          <t>918000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>876398</t>
+          <t>876537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>911286</t>
+          <t>911283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1774996</t>
+          <t>1777752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1821557</t>
+          <t>1821832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>65348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>75113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109851</t>
+          <t>108753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119015</t>
+          <t>119901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164223</t>
+          <t>165087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613205</t>
+          <t>613161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640627</t>
+          <t>641135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573990</t>
+          <t>575088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609893</t>
+          <t>608728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1198127</t>
+          <t>1197263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1243335</t>
+          <t>1242449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76144</t>
+          <t>77316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88290</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128241</t>
+          <t>129171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148349</t>
+          <t>143978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198406</t>
+          <t>195226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866078</t>
+          <t>864906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895242</t>
+          <t>896382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910371</t>
+          <t>909441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950322</t>
+          <t>948130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1782428</t>
+          <t>1785608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1832485</t>
+          <t>1836856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228714</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>353205</t>
+          <t>353412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>475327</t>
+          <t>473518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>557935</t>
+          <t>564186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3047829</t>
+          <t>3049425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3104581</t>
+          <t>3104622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3025992</t>
+          <t>3025785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3093722</t>
+          <t>3094942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6097806</t>
+          <t>6091555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6180414</t>
+          <t>6182223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62971</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126997</t>
+          <t>123556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131661</t>
+          <t>131057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182336</t>
+          <t>177986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640498</t>
+          <t>639839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668297</t>
+          <t>668555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>570053</t>
+          <t>573494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609437</t>
+          <t>611785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218183</t>
+          <t>1222533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1268858</t>
+          <t>1269462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65228</t>
+          <t>65381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102225</t>
+          <t>103338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140642</t>
+          <t>139459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188674</t>
+          <t>190334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>213839</t>
+          <t>214469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277072</t>
+          <t>274659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>914668</t>
+          <t>913555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>951665</t>
+          <t>951512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>843510</t>
+          <t>841850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>891542</t>
+          <t>892725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1772005</t>
+          <t>1774418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1835238</t>
+          <t>1834608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83496</t>
+          <t>83184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124041</t>
+          <t>122216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119903</t>
+          <t>120773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169374</t>
+          <t>169090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>699925</t>
+          <t>701198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729147</t>
+          <t>728034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652078</t>
+          <t>653903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>692623</t>
+          <t>692935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364368</t>
+          <t>1364652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1413839</t>
+          <t>1412969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55469</t>
+          <t>54451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87299</t>
+          <t>87922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129745</t>
+          <t>129064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176765</t>
+          <t>175231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194870</t>
+          <t>193000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252414</t>
+          <t>252066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>859503</t>
+          <t>858880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891333</t>
+          <t>892351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>874191</t>
+          <t>875725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>921211</t>
+          <t>921892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1745344</t>
+          <t>1745692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1802888</t>
+          <t>1804758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>211723</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274717</t>
+          <t>280066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480889</t>
+          <t>483844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>568669</t>
+          <t>565020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>710869</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>817586</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3150071</t>
+          <t>3144722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3213065</t>
+          <t>3209795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2987640</t>
+          <t>2991289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3075420</t>
+          <t>3072465</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6163511</t>
+          <t>6160143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6270228</t>
+          <t>6269347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53008</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69801</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104882</t>
+          <t>104098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>103611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>146455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621792</t>
+          <t>621343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>647199</t>
+          <t>646469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567957</t>
+          <t>568741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>603038</t>
+          <t>603743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1201669</t>
+          <t>1201184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1242803</t>
+          <t>1244028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>65298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103609</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150808</t>
+          <t>147211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153276</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206071</t>
+          <t>206334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>956158</t>
+          <t>957133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>984089</t>
+          <t>985418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892105</t>
+          <t>895702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939304</t>
+          <t>939964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1859273</t>
+          <t>1859010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1912068</t>
+          <t>1913434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62376</t>
+          <t>61873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83080</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123675</t>
+          <t>122658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125298</t>
+          <t>122878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172204</t>
+          <t>170601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>697176</t>
+          <t>697679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>726205</t>
+          <t>726801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>661336</t>
+          <t>662353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701931</t>
+          <t>700821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1372359</t>
+          <t>1373962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1419265</t>
+          <t>1421685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88795</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98989</t>
+          <t>97209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142255</t>
+          <t>142554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>164050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214921</t>
+          <t>217878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848772</t>
+          <t>848523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880961</t>
+          <t>882196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>901524</t>
+          <t>901225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944790</t>
+          <t>946570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1766425</t>
+          <t>1763468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1818352</t>
+          <t>1817296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179888</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236610</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390919</t>
+          <t>388455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>475836</t>
+          <t>477619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>595029</t>
+          <t>589503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>687165</t>
+          <t>686955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3157740</t>
+          <t>3158526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3214462</t>
+          <t>3215919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3068706</t>
+          <t>3066923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3153623</t>
+          <t>3156087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6251727</t>
+          <t>6251937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6343863</t>
+          <t>6349389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>78760</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>65450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84833</t>
+          <t>92837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>106778</t>
+          <t>116888</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90919</t>
+          <t>100753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123266</t>
+          <t>136124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>600550</t>
+          <t>652582</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>588180</t>
+          <t>638796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>610218</t>
+          <t>663055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>603241</t>
+          <t>653752</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>590296</t>
+          <t>639675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613980</t>
+          <t>667062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1203793</t>
+          <t>1306334</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1187305</t>
+          <t>1287098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219652</t>
+          <t>1322469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49308</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>43373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69567</t>
+          <t>70645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91170</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124205</t>
+          <t>138859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>156053</t>
+          <t>174202</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110231</t>
+          <t>150825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187596</t>
+          <t>199201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1143556</t>
+          <t>993593</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1123297</t>
+          <t>978272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169597</t>
+          <t>1005544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>850717</t>
+          <t>951269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>833257</t>
+          <t>931288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>866292</t>
+          <t>969222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1994273</t>
+          <t>1944863</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1962730</t>
+          <t>1919864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040095</t>
+          <t>1968240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957462</t>
+          <t>1070147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957462</t>
+          <t>1070147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957462</t>
+          <t>1070147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150326</t>
+          <t>2119065</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150326</t>
+          <t>2119065</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150326</t>
+          <t>2119065</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82571</t>
+          <t>86995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>97504</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37498</t>
+          <t>82472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114702</t>
+          <t>117701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>144459</t>
+          <t>162305</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94343</t>
+          <t>139559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175610</t>
+          <t>190461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643885</t>
+          <t>738272</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622109</t>
+          <t>716078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658810</t>
+          <t>752921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>849702</t>
+          <t>714755</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>818664</t>
+          <t>694558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>895868</t>
+          <t>729787</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1493587</t>
+          <t>1453027</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1462436</t>
+          <t>1424871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1543703</t>
+          <t>1475773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>54856</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41034</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>72015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>132704</t>
+          <t>142868</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105297</t>
+          <t>125925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156024</t>
+          <t>165100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>186701</t>
+          <t>197723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158660</t>
+          <t>173312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215668</t>
+          <t>221134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>871628</t>
+          <t>934004</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854798</t>
+          <t>916845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884591</t>
+          <t>947349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>961138</t>
+          <t>975019</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937818</t>
+          <t>952787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>988545</t>
+          <t>991962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1832766</t>
+          <t>1909025</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803799</t>
+          <t>1885614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1860807</t>
+          <t>1933436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093842</t>
+          <t>1117887</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093842</t>
+          <t>1117887</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093842</t>
+          <t>1117887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019467</t>
+          <t>2106748</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019467</t>
+          <t>2106748</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019467</t>
+          <t>2106748</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150804</t>
+          <t>185392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230107</t>
+          <t>243544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>323034</t>
+          <t>404522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>440327</t>
+          <t>472033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>514146</t>
+          <t>605652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>652784</t>
+          <t>698833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3259621</t>
+          <t>3318451</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3228504</t>
+          <t>3288016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3307807</t>
+          <t>3346168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3264798</t>
+          <t>3294797</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3219472</t>
+          <t>3260773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3336765</t>
+          <t>3328284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6524418</t>
+          <t>6613248</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6465625</t>
+          <t>6565533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6604263</t>
+          <t>6658714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>91,66%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
